--- a/src/test/resources/xlsx/2차전형점수.xlsx
+++ b/src/test/resources/xlsx/2차전형점수.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cabbage16\workspace\IdeaProjects\Bamdoliro\marubase\src\test\resources\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/test/resources/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E7A06F8-7E1E-4F26-B4D9-B4AF48F43C02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D97F83C-C548-4C41-8432-3AE5D7874EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1140" windowWidth="21600" windowHeight="11100" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>수험번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -80,27 +80,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>심층면접</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ncs</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>코딩 테스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>마이스터인재전형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기회균등전형</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>응시 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자기주도학습영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인성영역</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정원 외 전형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특별전형</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -111,7 +107,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;₩&quot;#,##0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -471,14 +467,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C8EB960-16E4-4546-BE22-CABF45F1D2EB}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -489,19 +485,16 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1001</v>
       </c>
@@ -512,17 +505,17 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>11.11</v>
+        <v>40</v>
       </c>
       <c r="E2">
-        <v>12.11</v>
-      </c>
-      <c r="G2" s="1" t="b" cm="1">
-        <f t="array" ref="G2">IF(C2="마이스터인재전형", IF(AND(ISBLANK(D2:F2)), FALSE, TRUE), IF(AND(ISBLANK(D2:E2)), FALSE, TRUE))</f>
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="b" cm="1">
+        <f t="array" ref="F2">IF(AND(ISBLANK(D2:E2)),FALSE,TRUE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>1002</v>
       </c>
@@ -532,12 +525,12 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="1" t="b" cm="1">
-        <f t="array" ref="G3">IF(C3="마이스터인재전형", IF(AND(ISBLANK(D3:F3)), FALSE, TRUE), IF(AND(ISBLANK(D3:E3)), FALSE, TRUE))</f>
+      <c r="F3" s="1" t="b" cm="1">
+        <f t="array" ref="F3">IF(AND(ISBLANK(D3:E3)),FALSE,TRUE)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -545,23 +538,20 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>11.11</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>11.11</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1" t="b" cm="1">
-        <f t="array" ref="G4">IF(C4="마이스터인재전형", IF(AND(ISBLANK(D4:F4)), FALSE, TRUE), IF(AND(ISBLANK(D4:E4)), FALSE, TRUE))</f>
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="b" cm="1">
+        <f t="array" ref="F4">IF(AND(ISBLANK(D4:E4)),FALSE,TRUE)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>3001</v>
       </c>
@@ -569,16 +559,16 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>111.11</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>22.11</v>
-      </c>
-      <c r="G5" s="1" t="b" cm="1">
-        <f t="array" ref="G5">IF(C5="마이스터인재전형", IF(AND(ISBLANK(D5:F5)), FALSE, TRUE), IF(AND(ISBLANK(D5:E5)), FALSE, TRUE))</f>
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="b" cm="1">
+        <f t="array" ref="F5">IF(AND(ISBLANK(D5:E5)),FALSE,TRUE)</f>
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/xlsx/2차전형점수.xlsx
+++ b/src/test/resources/xlsx/2차전형점수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/test/resources/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D97F83C-C548-4C41-8432-3AE5D7874EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC151166-4663-CF46-823C-ACFB055A5853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1140" windowWidth="21600" windowHeight="11100" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
     <t>수험번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -89,10 +89,6 @@
   </si>
   <si>
     <t>인성영역</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>정원 외 전형</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -538,7 +534,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4">
         <v>35</v>
@@ -553,7 +549,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>3001</v>
+        <v>2002</v>
       </c>
       <c r="B5" t="s">
         <v>2</v>

--- a/src/test/resources/xlsx/2차전형점수.xlsx
+++ b/src/test/resources/xlsx/2차전형점수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/test/resources/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC151166-4663-CF46-823C-ACFB055A5853}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD318E38-4078-5F49-9961-C8B5BD9D6ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1140" windowWidth="21600" windowHeight="11100" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
@@ -92,7 +92,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>특별전형</t>
+    <t>사회통합전형</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/src/test/resources/xlsx/2차전형점수.xlsx
+++ b/src/test/resources/xlsx/2차전형점수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/test/resources/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD318E38-4078-5F49-9961-C8B5BD9D6ED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7150EAE1-63D1-6443-BD06-2C8AFBF8CF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1140" windowWidth="21600" windowHeight="11100" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
@@ -60,10 +60,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
   <si>
-    <t>수험번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -93,6 +89,10 @@
   </si>
   <si>
     <t>사회통합전형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>면접번호</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,33 +472,33 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>1001</v>
+        <v>111001</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2">
         <v>40</v>
@@ -513,13 +513,13 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>1002</v>
+        <v>111002</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="1" t="b" cm="1">
         <f t="array" ref="F3">IF(AND(ISBLANK(D3:E3)),FALSE,TRUE)</f>
@@ -528,13 +528,13 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>2001</v>
+        <v>212001</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>35</v>
@@ -549,13 +549,13 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>2002</v>
+        <v>212002</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>10</v>

--- a/src/test/resources/xlsx/2차전형점수.xlsx
+++ b/src/test/resources/xlsx/2차전형점수.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hsm/Documents/백엔드/haeundae-marubase/src/test/resources/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7150EAE1-63D1-6443-BD06-2C8AFBF8CF38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69419A42-C4B8-684F-ADE6-D9259F53C6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1140" windowWidth="21600" windowHeight="11100" xr2:uid="{7690012B-BFFA-3C48-824D-509550F219F4}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -93,6 +93,22 @@
   </si>
   <si>
     <t>면접번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>111002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>212001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>212002</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -142,12 +158,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,8 +510,8 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2">
-        <v>111001</v>
+      <c r="A2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
@@ -512,8 +531,8 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3">
-        <v>111002</v>
+      <c r="A3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
@@ -527,8 +546,8 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4">
-        <v>212001</v>
+      <c r="A4" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
@@ -548,8 +567,8 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5">
-        <v>212002</v>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
